--- a/docs/Lab03/Lab03_WBT_TCs_Form.xlsx
+++ b/docs/Lab03/Lab03_WBT_TCs_Form.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10A8EF55-68EC-40F2-8A32-429E14F42013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C6146CC-C904-4EB5-A578-64F59E5B683B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="138">
   <si>
     <t>VVSS, Info Romana, 2025-2026</t>
   </si>
@@ -639,9 +639,6 @@
   </si>
   <si>
     <t>lapte = 50 passed</t>
-  </si>
-  <si>
-    <t>da</t>
   </si>
   <si>
     <t>Lucaci George</t>
@@ -1470,6 +1467,66 @@
     <xf numFmtId="0" fontId="7" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1509,9 +1566,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1533,67 +1587,19 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1605,9 +1611,6 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1635,9 +1638,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1653,8 +1653,20 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1684,21 +1696,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2109,12 +2106,12 @@
   <sheetData>
     <row r="1" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B1" s="12"/>
-      <c r="D1" s="47" t="s">
+      <c r="D1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="49"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="69"/>
     </row>
     <row r="2" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B2" s="36" t="s">
@@ -2162,7 +2159,7 @@
         <v>9</v>
       </c>
       <c r="O7" s="26" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P7" s="26">
         <v>234</v>
@@ -2177,7 +2174,7 @@
         <v>10</v>
       </c>
       <c r="O8" s="26" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="P8" s="26">
         <v>233</v>
@@ -2246,73 +2243,73 @@
   <sheetData>
     <row r="1" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B1" s="12"/>
-      <c r="D1" s="47" t="s">
+      <c r="D1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="49"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="69"/>
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B3" s="89" t="s">
+      <c r="B3" s="92" t="s">
         <v>81</v>
       </c>
-      <c r="C3" s="90"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="90"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="90"/>
-      <c r="I3" s="90"/>
-      <c r="J3" s="90"/>
-      <c r="K3" s="91"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="93"/>
+      <c r="K3" s="94"/>
     </row>
     <row r="6" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B6" s="47" t="s">
+      <c r="B6" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="49"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="69"/>
       <c r="F6" s="29"/>
       <c r="G6" s="29"/>
-      <c r="I6" s="47" t="s">
+      <c r="I6" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48"/>
-      <c r="L6" s="48"/>
-      <c r="M6" s="48"/>
-      <c r="N6" s="48"/>
-      <c r="O6" s="48"/>
-      <c r="Q6" s="47" t="s">
+      <c r="J6" s="68"/>
+      <c r="K6" s="68"/>
+      <c r="L6" s="68"/>
+      <c r="M6" s="68"/>
+      <c r="N6" s="68"/>
+      <c r="O6" s="68"/>
+      <c r="Q6" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="R6" s="48"/>
-      <c r="S6" s="48"/>
-      <c r="T6" s="48"/>
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="68"/>
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B8" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="103" t="s">
+      <c r="C8" s="104" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="103"/>
-      <c r="E8" s="103"/>
+      <c r="D8" s="104"/>
+      <c r="E8" s="104"/>
       <c r="F8" s="31"/>
       <c r="G8" s="31"/>
       <c r="I8" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="Q8" s="102" t="s">
+      <c r="Q8" s="89" t="s">
         <v>19</v>
       </c>
-      <c r="R8" s="102"/>
-      <c r="S8" s="102"/>
+      <c r="R8" s="89"/>
+      <c r="S8" s="89"/>
       <c r="T8" s="32">
         <v>5</v>
       </c>
@@ -2321,19 +2318,19 @@
       <c r="B9" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="92" t="s">
+      <c r="C9" s="88" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="92"/>
-      <c r="E9" s="92"/>
+      <c r="D9" s="88"/>
+      <c r="E9" s="88"/>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
       <c r="I9" s="35"/>
-      <c r="Q9" s="102" t="s">
+      <c r="Q9" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="R9" s="102"/>
-      <c r="S9" s="102"/>
+      <c r="R9" s="89"/>
+      <c r="S9" s="89"/>
       <c r="T9" s="40" t="s">
         <v>83</v>
       </c>
@@ -2342,29 +2339,29 @@
       <c r="B10" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="92" t="s">
+      <c r="C10" s="88" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="92"/>
-      <c r="E10" s="92"/>
+      <c r="D10" s="88"/>
+      <c r="E10" s="88"/>
       <c r="F10" s="34"/>
       <c r="G10" s="34"/>
-      <c r="I10" s="93" t="s">
+      <c r="I10" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="J10" s="94"/>
-      <c r="K10" s="94"/>
-      <c r="L10" s="94"/>
-      <c r="M10" s="94"/>
-      <c r="N10" s="94"/>
-      <c r="O10" s="95"/>
-      <c r="Q10" s="102" t="s">
+      <c r="J10" s="96"/>
+      <c r="K10" s="96"/>
+      <c r="L10" s="96"/>
+      <c r="M10" s="96"/>
+      <c r="N10" s="96"/>
+      <c r="O10" s="97"/>
+      <c r="Q10" s="89" t="s">
         <v>25</v>
       </c>
-      <c r="R10" s="102" t="s">
+      <c r="R10" s="89" t="s">
         <v>26</v>
       </c>
-      <c r="S10" s="102"/>
+      <c r="S10" s="89"/>
       <c r="T10" s="32" t="s">
         <v>82</v>
       </c>
@@ -2373,143 +2370,143 @@
       <c r="B11" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="92" t="s">
+      <c r="C11" s="88" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="92"/>
-      <c r="E11" s="92"/>
+      <c r="D11" s="88"/>
+      <c r="E11" s="88"/>
       <c r="F11" s="34"/>
       <c r="G11" s="34"/>
-      <c r="I11" s="96"/>
-      <c r="J11" s="97"/>
-      <c r="K11" s="97"/>
-      <c r="L11" s="97"/>
-      <c r="M11" s="97"/>
-      <c r="N11" s="97"/>
-      <c r="O11" s="98"/>
+      <c r="I11" s="98"/>
+      <c r="J11" s="99"/>
+      <c r="K11" s="99"/>
+      <c r="L11" s="99"/>
+      <c r="M11" s="99"/>
+      <c r="N11" s="99"/>
+      <c r="O11" s="100"/>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B12" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="92" t="s">
+      <c r="C12" s="88" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="92"/>
-      <c r="E12" s="92"/>
+      <c r="D12" s="88"/>
+      <c r="E12" s="88"/>
       <c r="F12" s="34"/>
       <c r="G12" s="34"/>
-      <c r="I12" s="96"/>
-      <c r="J12" s="97"/>
-      <c r="K12" s="97"/>
-      <c r="L12" s="97"/>
-      <c r="M12" s="97"/>
-      <c r="N12" s="97"/>
-      <c r="O12" s="98"/>
+      <c r="I12" s="98"/>
+      <c r="J12" s="99"/>
+      <c r="K12" s="99"/>
+      <c r="L12" s="99"/>
+      <c r="M12" s="99"/>
+      <c r="N12" s="99"/>
+      <c r="O12" s="100"/>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B13" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="92" t="s">
+      <c r="C13" s="88" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="92"/>
-      <c r="E13" s="92"/>
+      <c r="D13" s="88"/>
+      <c r="E13" s="88"/>
       <c r="F13" s="34"/>
       <c r="G13" s="34"/>
-      <c r="I13" s="96"/>
-      <c r="J13" s="97"/>
-      <c r="K13" s="97"/>
-      <c r="L13" s="97"/>
-      <c r="M13" s="97"/>
-      <c r="N13" s="97"/>
-      <c r="O13" s="98"/>
-      <c r="Q13" s="47" t="s">
+      <c r="I13" s="98"/>
+      <c r="J13" s="99"/>
+      <c r="K13" s="99"/>
+      <c r="L13" s="99"/>
+      <c r="M13" s="99"/>
+      <c r="N13" s="99"/>
+      <c r="O13" s="100"/>
+      <c r="Q13" s="67" t="s">
         <v>30</v>
       </c>
-      <c r="R13" s="48"/>
-      <c r="S13" s="48"/>
-      <c r="T13" s="48"/>
+      <c r="R13" s="68"/>
+      <c r="S13" s="68"/>
+      <c r="T13" s="68"/>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B14" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="92" t="s">
+      <c r="C14" s="88" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="92"/>
-      <c r="E14" s="92"/>
+      <c r="D14" s="88"/>
+      <c r="E14" s="88"/>
       <c r="F14" s="34"/>
       <c r="G14" s="34"/>
-      <c r="I14" s="96"/>
-      <c r="J14" s="97"/>
-      <c r="K14" s="97"/>
-      <c r="L14" s="97"/>
-      <c r="M14" s="97"/>
-      <c r="N14" s="97"/>
-      <c r="O14" s="98"/>
+      <c r="I14" s="98"/>
+      <c r="J14" s="99"/>
+      <c r="K14" s="99"/>
+      <c r="L14" s="99"/>
+      <c r="M14" s="99"/>
+      <c r="N14" s="99"/>
+      <c r="O14" s="100"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="I15" s="96"/>
-      <c r="J15" s="97"/>
-      <c r="K15" s="97"/>
-      <c r="L15" s="97"/>
-      <c r="M15" s="97"/>
-      <c r="N15" s="97"/>
-      <c r="O15" s="98"/>
+      <c r="I15" s="98"/>
+      <c r="J15" s="99"/>
+      <c r="K15" s="99"/>
+      <c r="L15" s="99"/>
+      <c r="M15" s="99"/>
+      <c r="N15" s="99"/>
+      <c r="O15" s="100"/>
       <c r="Q15" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="R15" s="103" t="s">
+      <c r="R15" s="104" t="s">
         <v>32</v>
       </c>
-      <c r="S15" s="103"/>
-      <c r="T15" s="103"/>
+      <c r="S15" s="104"/>
+      <c r="T15" s="104"/>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="I16" s="96"/>
-      <c r="J16" s="97"/>
-      <c r="K16" s="97"/>
-      <c r="L16" s="97"/>
-      <c r="M16" s="97"/>
-      <c r="N16" s="97"/>
-      <c r="O16" s="98"/>
+      <c r="I16" s="98"/>
+      <c r="J16" s="99"/>
+      <c r="K16" s="99"/>
+      <c r="L16" s="99"/>
+      <c r="M16" s="99"/>
+      <c r="N16" s="99"/>
+      <c r="O16" s="100"/>
       <c r="Q16" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="R16" s="108" t="s">
+      <c r="R16" s="90" t="s">
         <v>84</v>
       </c>
-      <c r="S16" s="108"/>
-      <c r="T16" s="108"/>
+      <c r="S16" s="90"/>
+      <c r="T16" s="90"/>
     </row>
     <row r="17" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I17" s="96"/>
-      <c r="J17" s="97"/>
-      <c r="K17" s="97"/>
-      <c r="L17" s="97"/>
-      <c r="M17" s="97"/>
-      <c r="N17" s="97"/>
-      <c r="O17" s="98"/>
+      <c r="I17" s="98"/>
+      <c r="J17" s="99"/>
+      <c r="K17" s="99"/>
+      <c r="L17" s="99"/>
+      <c r="M17" s="99"/>
+      <c r="N17" s="99"/>
+      <c r="O17" s="100"/>
       <c r="Q17" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="R17" s="104" t="s">
+      <c r="R17" s="105" t="s">
         <v>85</v>
       </c>
-      <c r="S17" s="104"/>
-      <c r="T17" s="104"/>
+      <c r="S17" s="105"/>
+      <c r="T17" s="105"/>
     </row>
     <row r="18" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I18" s="96"/>
-      <c r="J18" s="97"/>
-      <c r="K18" s="97"/>
-      <c r="L18" s="97"/>
-      <c r="M18" s="97"/>
-      <c r="N18" s="97"/>
-      <c r="O18" s="98"/>
+      <c r="I18" s="98"/>
+      <c r="J18" s="99"/>
+      <c r="K18" s="99"/>
+      <c r="L18" s="99"/>
+      <c r="M18" s="99"/>
+      <c r="N18" s="99"/>
+      <c r="O18" s="100"/>
       <c r="Q18" s="33" t="s">
         <v>35</v>
       </c>
@@ -2520,30 +2517,30 @@
       <c r="T18" s="87"/>
     </row>
     <row r="19" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I19" s="96"/>
-      <c r="J19" s="97"/>
-      <c r="K19" s="97"/>
-      <c r="L19" s="97"/>
-      <c r="M19" s="97"/>
-      <c r="N19" s="97"/>
-      <c r="O19" s="98"/>
+      <c r="I19" s="98"/>
+      <c r="J19" s="99"/>
+      <c r="K19" s="99"/>
+      <c r="L19" s="99"/>
+      <c r="M19" s="99"/>
+      <c r="N19" s="99"/>
+      <c r="O19" s="100"/>
       <c r="Q19" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="R19" s="105" t="s">
+      <c r="R19" s="106" t="s">
         <v>87</v>
       </c>
-      <c r="S19" s="106"/>
-      <c r="T19" s="107"/>
+      <c r="S19" s="107"/>
+      <c r="T19" s="108"/>
     </row>
     <row r="20" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I20" s="96"/>
-      <c r="J20" s="97"/>
-      <c r="K20" s="97"/>
-      <c r="L20" s="97"/>
-      <c r="M20" s="97"/>
-      <c r="N20" s="97"/>
-      <c r="O20" s="98"/>
+      <c r="I20" s="98"/>
+      <c r="J20" s="99"/>
+      <c r="K20" s="99"/>
+      <c r="L20" s="99"/>
+      <c r="M20" s="99"/>
+      <c r="N20" s="99"/>
+      <c r="O20" s="100"/>
       <c r="Q20" s="33" t="s">
         <v>90</v>
       </c>
@@ -2554,55 +2551,47 @@
       <c r="T20" s="87"/>
     </row>
     <row r="21" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I21" s="96"/>
-      <c r="J21" s="97"/>
-      <c r="K21" s="97"/>
-      <c r="L21" s="97"/>
-      <c r="M21" s="97"/>
-      <c r="N21" s="97"/>
-      <c r="O21" s="98"/>
+      <c r="I21" s="98"/>
+      <c r="J21" s="99"/>
+      <c r="K21" s="99"/>
+      <c r="L21" s="99"/>
+      <c r="M21" s="99"/>
+      <c r="N21" s="99"/>
+      <c r="O21" s="100"/>
       <c r="Q21" s="33"/>
-      <c r="R21" s="88"/>
-      <c r="S21" s="88"/>
-      <c r="T21" s="88"/>
+      <c r="R21" s="91"/>
+      <c r="S21" s="91"/>
+      <c r="T21" s="91"/>
     </row>
     <row r="22" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I22" s="96"/>
-      <c r="J22" s="97"/>
-      <c r="K22" s="97"/>
-      <c r="L22" s="97"/>
-      <c r="M22" s="97"/>
-      <c r="N22" s="97"/>
-      <c r="O22" s="98"/>
+      <c r="I22" s="98"/>
+      <c r="J22" s="99"/>
+      <c r="K22" s="99"/>
+      <c r="L22" s="99"/>
+      <c r="M22" s="99"/>
+      <c r="N22" s="99"/>
+      <c r="O22" s="100"/>
     </row>
     <row r="23" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I23" s="96"/>
-      <c r="J23" s="97"/>
-      <c r="K23" s="97"/>
-      <c r="L23" s="97"/>
-      <c r="M23" s="97"/>
-      <c r="N23" s="97"/>
-      <c r="O23" s="98"/>
+      <c r="I23" s="98"/>
+      <c r="J23" s="99"/>
+      <c r="K23" s="99"/>
+      <c r="L23" s="99"/>
+      <c r="M23" s="99"/>
+      <c r="N23" s="99"/>
+      <c r="O23" s="100"/>
     </row>
     <row r="24" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I24" s="99"/>
-      <c r="J24" s="100"/>
-      <c r="K24" s="100"/>
-      <c r="L24" s="100"/>
-      <c r="M24" s="100"/>
-      <c r="N24" s="100"/>
-      <c r="O24" s="101"/>
+      <c r="I24" s="101"/>
+      <c r="J24" s="102"/>
+      <c r="K24" s="102"/>
+      <c r="L24" s="102"/>
+      <c r="M24" s="102"/>
+      <c r="N24" s="102"/>
+      <c r="O24" s="103"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="R18:T18"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="Q13:T13"/>
-    <mergeCell ref="C14:E14"/>
     <mergeCell ref="D1:I1"/>
     <mergeCell ref="R20:T20"/>
     <mergeCell ref="R21:T21"/>
@@ -2619,6 +2608,14 @@
     <mergeCell ref="Q6:T6"/>
     <mergeCell ref="R17:T17"/>
     <mergeCell ref="R19:T19"/>
+    <mergeCell ref="R18:T18"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="Q13:T13"/>
+    <mergeCell ref="C14:E14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2657,164 +2654,164 @@
   <sheetData>
     <row r="1" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B1" s="12"/>
-      <c r="D1" s="47" t="s">
+      <c r="D1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="49"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="69"/>
     </row>
     <row r="3" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B3" s="113" t="s">
+      <c r="B3" s="118" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="114"/>
-      <c r="D3" s="114"/>
-      <c r="E3" s="114"/>
-      <c r="F3" s="115"/>
+      <c r="C3" s="119"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="119"/>
+      <c r="F3" s="120"/>
     </row>
     <row r="5" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="2:28" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="121" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="116" t="s">
+      <c r="C6" s="121" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="117" t="s">
+      <c r="D6" s="122" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="116" t="s">
+      <c r="E6" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="116"/>
-      <c r="G6" s="116"/>
-      <c r="H6" s="116"/>
-      <c r="I6" s="116"/>
-      <c r="J6" s="116"/>
-      <c r="K6" s="116"/>
-      <c r="L6" s="116"/>
-      <c r="M6" s="116"/>
-      <c r="N6" s="116"/>
-      <c r="O6" s="116"/>
-      <c r="P6" s="116"/>
-      <c r="Q6" s="116"/>
-      <c r="R6" s="116"/>
-      <c r="S6" s="116"/>
-      <c r="T6" s="116"/>
-      <c r="U6" s="116"/>
-      <c r="V6" s="116"/>
-      <c r="W6" s="116"/>
-      <c r="X6" s="116"/>
-      <c r="Y6" s="116"/>
-      <c r="Z6" s="116"/>
-      <c r="AA6" s="116"/>
-      <c r="AB6" s="116"/>
+      <c r="F6" s="121"/>
+      <c r="G6" s="121"/>
+      <c r="H6" s="121"/>
+      <c r="I6" s="121"/>
+      <c r="J6" s="121"/>
+      <c r="K6" s="121"/>
+      <c r="L6" s="121"/>
+      <c r="M6" s="121"/>
+      <c r="N6" s="121"/>
+      <c r="O6" s="121"/>
+      <c r="P6" s="121"/>
+      <c r="Q6" s="121"/>
+      <c r="R6" s="121"/>
+      <c r="S6" s="121"/>
+      <c r="T6" s="121"/>
+      <c r="U6" s="121"/>
+      <c r="V6" s="121"/>
+      <c r="W6" s="121"/>
+      <c r="X6" s="121"/>
+      <c r="Y6" s="121"/>
+      <c r="Z6" s="121"/>
+      <c r="AA6" s="121"/>
+      <c r="AB6" s="121"/>
     </row>
     <row r="7" spans="2:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="116"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="118"/>
-      <c r="E7" s="123" t="s">
+      <c r="B7" s="121"/>
+      <c r="C7" s="121"/>
+      <c r="D7" s="123"/>
+      <c r="E7" s="111" t="s">
         <v>40</v>
       </c>
-      <c r="F7" s="122" t="s">
+      <c r="F7" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="G7" s="122"/>
-      <c r="H7" s="122"/>
-      <c r="I7" s="122"/>
-      <c r="J7" s="122"/>
-      <c r="K7" s="122"/>
-      <c r="L7" s="122"/>
-      <c r="M7" s="122"/>
-      <c r="N7" s="122"/>
-      <c r="O7" s="122"/>
-      <c r="P7" s="109" t="s">
+      <c r="G7" s="112"/>
+      <c r="H7" s="112"/>
+      <c r="I7" s="112"/>
+      <c r="J7" s="112"/>
+      <c r="K7" s="112"/>
+      <c r="L7" s="112"/>
+      <c r="M7" s="112"/>
+      <c r="N7" s="112"/>
+      <c r="O7" s="112"/>
+      <c r="P7" s="114" t="s">
         <v>42</v>
       </c>
-      <c r="Q7" s="109"/>
-      <c r="R7" s="109"/>
-      <c r="S7" s="109"/>
-      <c r="T7" s="109"/>
-      <c r="U7" s="109"/>
-      <c r="V7" s="119" t="s">
+      <c r="Q7" s="114"/>
+      <c r="R7" s="114"/>
+      <c r="S7" s="114"/>
+      <c r="T7" s="114"/>
+      <c r="U7" s="114"/>
+      <c r="V7" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="W7" s="119"/>
-      <c r="X7" s="119"/>
-      <c r="Y7" s="119"/>
-      <c r="Z7" s="119"/>
-      <c r="AA7" s="119"/>
-      <c r="AB7" s="119"/>
+      <c r="W7" s="113"/>
+      <c r="X7" s="113"/>
+      <c r="Y7" s="113"/>
+      <c r="Z7" s="113"/>
+      <c r="AA7" s="113"/>
+      <c r="AB7" s="113"/>
     </row>
     <row r="8" spans="2:28" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="116"/>
-      <c r="C8" s="120" t="s">
+      <c r="B8" s="121"/>
+      <c r="C8" s="109" t="s">
         <v>96</v>
       </c>
-      <c r="D8" s="120"/>
-      <c r="E8" s="123"/>
-      <c r="F8" s="122" t="s">
+      <c r="D8" s="109"/>
+      <c r="E8" s="111"/>
+      <c r="F8" s="112" t="s">
         <v>91</v>
       </c>
-      <c r="G8" s="122"/>
-      <c r="H8" s="122" t="s">
+      <c r="G8" s="112"/>
+      <c r="H8" s="112" t="s">
         <v>92</v>
       </c>
-      <c r="I8" s="122"/>
-      <c r="J8" s="122" t="s">
+      <c r="I8" s="112"/>
+      <c r="J8" s="112" t="s">
         <v>93</v>
       </c>
-      <c r="K8" s="122"/>
-      <c r="L8" s="122" t="s">
+      <c r="K8" s="112"/>
+      <c r="L8" s="112" t="s">
         <v>94</v>
       </c>
-      <c r="M8" s="122"/>
-      <c r="N8" s="109" t="s">
+      <c r="M8" s="112"/>
+      <c r="N8" s="114" t="s">
         <v>33</v>
       </c>
-      <c r="O8" s="109" t="s">
+      <c r="O8" s="114" t="s">
         <v>34</v>
       </c>
-      <c r="P8" s="109" t="s">
+      <c r="P8" s="114" t="s">
         <v>35</v>
       </c>
-      <c r="Q8" s="109" t="s">
+      <c r="Q8" s="114" t="s">
         <v>89</v>
       </c>
-      <c r="R8" s="109" t="s">
+      <c r="R8" s="114" t="s">
         <v>90</v>
       </c>
-      <c r="S8" s="119">
+      <c r="S8" s="113">
         <v>0</v>
       </c>
-      <c r="T8" s="119">
+      <c r="T8" s="113">
         <v>1</v>
       </c>
-      <c r="U8" s="119">
+      <c r="U8" s="113">
         <v>2</v>
       </c>
-      <c r="V8" s="119" t="s">
+      <c r="V8" s="113" t="s">
         <v>44</v>
       </c>
-      <c r="W8" s="119" t="s">
+      <c r="W8" s="113" t="s">
         <v>45</v>
       </c>
-      <c r="X8" s="119" t="s">
+      <c r="X8" s="113" t="s">
         <v>46</v>
       </c>
-      <c r="Y8" s="119" t="s">
+      <c r="Y8" s="113" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="9" spans="2:28" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B9" s="116"/>
-      <c r="C9" s="121"/>
-      <c r="D9" s="121"/>
-      <c r="E9" s="123"/>
+      <c r="B9" s="121"/>
+      <c r="C9" s="110"/>
+      <c r="D9" s="110"/>
+      <c r="E9" s="111"/>
       <c r="F9" s="13" t="s">
         <v>48</v>
       </c>
@@ -2839,18 +2836,18 @@
       <c r="M9" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="N9" s="109"/>
-      <c r="O9" s="109"/>
-      <c r="P9" s="109"/>
-      <c r="Q9" s="109"/>
-      <c r="R9" s="109"/>
-      <c r="S9" s="119"/>
-      <c r="T9" s="119"/>
-      <c r="U9" s="119"/>
-      <c r="V9" s="119"/>
-      <c r="W9" s="119"/>
-      <c r="X9" s="119"/>
-      <c r="Y9" s="119"/>
+      <c r="N9" s="114"/>
+      <c r="O9" s="114"/>
+      <c r="P9" s="114"/>
+      <c r="Q9" s="114"/>
+      <c r="R9" s="114"/>
+      <c r="S9" s="113"/>
+      <c r="T9" s="113"/>
+      <c r="U9" s="113"/>
+      <c r="V9" s="113"/>
+      <c r="W9" s="113"/>
+      <c r="X9" s="113"/>
+      <c r="Y9" s="113"/>
     </row>
     <row r="10" spans="2:28" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="14" t="s">
@@ -3081,9 +3078,9 @@
       <c r="I15" s="17"/>
       <c r="J15" s="17"/>
       <c r="K15" s="17"/>
-      <c r="L15" s="110"/>
-      <c r="M15" s="111"/>
-      <c r="N15" s="112"/>
+      <c r="L15" s="115"/>
+      <c r="M15" s="116"/>
+      <c r="N15" s="117"/>
       <c r="O15" s="17"/>
       <c r="P15" s="18"/>
       <c r="Q15" s="18"/>
@@ -3104,6 +3101,19 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:AB6"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="E7:E9"/>
     <mergeCell ref="F7:O7"/>
@@ -3120,19 +3130,6 @@
     <mergeCell ref="P7:U7"/>
     <mergeCell ref="N8:N9"/>
     <mergeCell ref="O8:O9"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="D1:G1"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:AB6"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3162,55 +3159,55 @@
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B1" s="12"/>
-      <c r="D1" s="47" t="s">
+      <c r="D1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="49"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="69"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="70" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="50"/>
-      <c r="K3" s="50"/>
-      <c r="L3" s="50"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="70"/>
+      <c r="I3" s="70"/>
+      <c r="J3" s="70"/>
+      <c r="K3" s="70"/>
+      <c r="L3" s="70"/>
     </row>
     <row r="4" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="51" t="s">
+      <c r="B4" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="60" t="s">
+      <c r="C4" s="62" t="s">
         <v>53</v>
       </c>
-      <c r="D4" s="62" t="s">
+      <c r="D4" s="81" t="s">
         <v>54</v>
       </c>
-      <c r="E4" s="53" t="s">
+      <c r="E4" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="F4" s="59"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59"/>
-      <c r="J4" s="54"/>
-      <c r="K4" s="53" t="s">
+      <c r="F4" s="79"/>
+      <c r="G4" s="79"/>
+      <c r="H4" s="79"/>
+      <c r="I4" s="79"/>
+      <c r="J4" s="74"/>
+      <c r="K4" s="73" t="s">
         <v>56</v>
       </c>
-      <c r="L4" s="54"/>
+      <c r="L4" s="74"/>
     </row>
     <row r="5" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="52"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="63"/>
+      <c r="B5" s="72"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="82"/>
       <c r="E5" s="2" t="s">
         <v>115</v>
       </c>
@@ -3223,10 +3220,10 @@
       <c r="H5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I5" s="55" t="s">
+      <c r="I5" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="J5" s="56"/>
+      <c r="J5" s="76"/>
       <c r="K5" s="2" t="s">
         <v>57</v>
       </c>
@@ -3238,7 +3235,7 @@
       <c r="B6" s="21">
         <v>9</v>
       </c>
-      <c r="C6" s="57" t="s">
+      <c r="C6" s="77" t="s">
         <v>59</v>
       </c>
       <c r="D6" s="4" t="s">
@@ -3256,10 +3253,10 @@
       <c r="H6" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="I6" s="64" t="s">
+      <c r="I6" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="J6" s="65"/>
+      <c r="J6" s="84"/>
       <c r="K6" s="37" t="s">
         <v>118</v>
       </c>
@@ -3271,7 +3268,7 @@
       <c r="B7" s="21">
         <v>10</v>
       </c>
-      <c r="C7" s="57"/>
+      <c r="C7" s="77"/>
       <c r="D7" s="4" t="s">
         <v>60</v>
       </c>
@@ -3287,10 +3284,10 @@
       <c r="H7" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="I7" s="53" t="s">
+      <c r="I7" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="J7" s="54"/>
+      <c r="J7" s="74"/>
       <c r="K7" s="21" t="s">
         <v>121</v>
       </c>
@@ -3302,7 +3299,7 @@
       <c r="B8" s="21">
         <v>11</v>
       </c>
-      <c r="C8" s="57"/>
+      <c r="C8" s="77"/>
       <c r="D8" s="10" t="s">
         <v>123</v>
       </c>
@@ -3318,10 +3315,10 @@
       <c r="H8" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="I8" s="53" t="s">
+      <c r="I8" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="J8" s="54"/>
+      <c r="J8" s="74"/>
       <c r="K8" s="38" t="s">
         <v>126</v>
       </c>
@@ -3333,7 +3330,7 @@
       <c r="B9" s="21">
         <v>12</v>
       </c>
-      <c r="C9" s="57"/>
+      <c r="C9" s="77"/>
       <c r="D9" s="10" t="s">
         <v>128</v>
       </c>
@@ -3349,10 +3346,10 @@
       <c r="H9" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="I9" s="53" t="s">
+      <c r="I9" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="J9" s="54"/>
+      <c r="J9" s="74"/>
       <c r="K9" s="38" t="s">
         <v>130</v>
       </c>
@@ -3364,7 +3361,7 @@
       <c r="B10" s="2">
         <v>13</v>
       </c>
-      <c r="C10" s="58"/>
+      <c r="C10" s="78"/>
       <c r="D10" s="9" t="s">
         <v>132</v>
       </c>
@@ -3380,10 +3377,10 @@
       <c r="H10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I10" s="55" t="s">
+      <c r="I10" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="J10" s="56"/>
+      <c r="J10" s="76"/>
       <c r="K10" s="2" t="s">
         <v>134</v>
       </c>
@@ -3417,84 +3414,84 @@
       <c r="C13" s="46"/>
       <c r="D13" s="46"/>
       <c r="E13" s="46"/>
-      <c r="F13" s="66" t="s">
+      <c r="F13" s="85" t="s">
         <v>63</v>
       </c>
-      <c r="G13" s="67"/>
+      <c r="G13" s="86"/>
       <c r="H13" s="45" t="s">
         <v>64</v>
       </c>
       <c r="I13" s="46"/>
       <c r="J13" s="46"/>
       <c r="K13" s="46"/>
-      <c r="L13" s="76"/>
-      <c r="M13" s="81" t="s">
+      <c r="L13" s="47"/>
+      <c r="M13" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="N13" s="82"/>
+      <c r="N13" s="53"/>
     </row>
     <row r="14" spans="2:14" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="80" t="s">
+      <c r="B14" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="72" t="s">
+      <c r="C14" s="55" t="s">
         <v>67</v>
       </c>
-      <c r="D14" s="72" t="s">
+      <c r="D14" s="55" t="s">
         <v>68</v>
       </c>
-      <c r="E14" s="84" t="s">
+      <c r="E14" s="57" t="s">
         <v>69</v>
       </c>
-      <c r="F14" s="69" t="s">
+      <c r="F14" s="59" t="s">
         <v>70</v>
       </c>
-      <c r="G14" s="68" t="s">
+      <c r="G14" s="61" t="s">
         <v>71</v>
       </c>
-      <c r="H14" s="70" t="s">
+      <c r="H14" s="63" t="s">
         <v>72</v>
       </c>
-      <c r="I14" s="72" t="s">
+      <c r="I14" s="55" t="s">
         <v>66</v>
       </c>
-      <c r="J14" s="72" t="s">
+      <c r="J14" s="55" t="s">
         <v>67</v>
       </c>
-      <c r="K14" s="74" t="s">
+      <c r="K14" s="65" t="s">
         <v>73</v>
       </c>
-      <c r="L14" s="77" t="s">
+      <c r="L14" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="M14" s="79" t="s">
+      <c r="M14" s="50" t="s">
         <v>75</v>
       </c>
-      <c r="N14" s="60" t="s">
+      <c r="N14" s="62" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B15" s="83"/>
-      <c r="C15" s="73"/>
-      <c r="D15" s="73"/>
-      <c r="E15" s="85"/>
-      <c r="F15" s="86"/>
-      <c r="G15" s="68"/>
-      <c r="H15" s="71"/>
-      <c r="I15" s="73"/>
-      <c r="J15" s="73"/>
-      <c r="K15" s="75"/>
-      <c r="L15" s="78"/>
-      <c r="M15" s="80"/>
-      <c r="N15" s="69"/>
+      <c r="B15" s="54"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="64"/>
+      <c r="I15" s="56"/>
+      <c r="J15" s="56"/>
+      <c r="K15" s="66"/>
+      <c r="L15" s="49"/>
+      <c r="M15" s="51"/>
+      <c r="N15" s="59"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B16" s="26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16" s="24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" s="24">
         <v>0</v>
@@ -3507,13 +3504,13 @@
         <v>77</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="I16" s="26">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J16" s="24">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K16" s="27">
         <v>0</v>
@@ -3530,6 +3527,21 @@
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="C6:C10"/>
+    <mergeCell ref="E4:J4"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I8:J8"/>
     <mergeCell ref="H13:L13"/>
     <mergeCell ref="L14:L15"/>
     <mergeCell ref="M14:M15"/>
@@ -3546,21 +3558,6 @@
     <mergeCell ref="K14:K15"/>
     <mergeCell ref="J14:J15"/>
     <mergeCell ref="B13:E13"/>
-    <mergeCell ref="D1:G1"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="C6:C10"/>
-    <mergeCell ref="E4:J4"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="F13:G13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3568,26 +3565,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="301f98df-4edd-4096-94f8-2f8af3eee570">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="cbfc0213-1ef7-4e52-9599-c30bc1b3f3d7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E819BB071F23F542A5DF0E9C9037AD04" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="08d9df77a39a0ee87f79f9436c57bbce">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="301f98df-4edd-4096-94f8-2f8af3eee570" xmlns:ns3="cbfc0213-1ef7-4e52-9599-c30bc1b3f3d7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="03dd79bc1474883a2d909db85c328b07" ns2:_="" ns3:_="">
     <xsd:import namespace="301f98df-4edd-4096-94f8-2f8af3eee570"/>
@@ -3776,26 +3753,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA2F5940-EC19-4D08-A8C2-FA31EF734077}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="301f98df-4edd-4096-94f8-2f8af3eee570"/>
-    <ds:schemaRef ds:uri="cbfc0213-1ef7-4e52-9599-c30bc1b3f3d7"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EECFCB93-350B-4228-B7F4-DB12383611F2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="301f98df-4edd-4096-94f8-2f8af3eee570">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="cbfc0213-1ef7-4e52-9599-c30bc1b3f3d7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B359A3C-84EA-4FDD-BB5C-023A91F35CC6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3812,4 +3790,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EECFCB93-350B-4228-B7F4-DB12383611F2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA2F5940-EC19-4D08-A8C2-FA31EF734077}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="301f98df-4edd-4096-94f8-2f8af3eee570"/>
+    <ds:schemaRef ds:uri="cbfc0213-1ef7-4e52-9599-c30bc1b3f3d7"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>